--- a/ExcelRAddIn/Tests/Stringfest Examples/R in Excel - (More) Forecasting.xlsx
+++ b/ExcelRAddIn/Tests/Stringfest Examples/R in Excel - (More) Forecasting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\Stringfest Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F0FE58-8C5B-4BA2-A60D-7613D91E572B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16955EB-5B14-4AA6-BD94-0B4201C0AA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{EB0856D8-E191-4F16-B73A-E50C554CDF02}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{EB0856D8-E191-4F16-B73A-E50C554CDF02}"/>
   </bookViews>
   <sheets>
     <sheet name="References" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="str">
-        <v>Jan 13</v>
+        <v>145</v>
       </c>
       <c r="C14" s="7">
         <v>460.30277779828714</v>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="str">
-        <v>Feb 13</v>
+        <v>146</v>
       </c>
       <c r="C15" s="7">
         <v>460.30277779828714</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="str">
-        <v>Mar 13</v>
+        <v>147</v>
       </c>
       <c r="C16" s="7">
         <v>460.30277779828714</v>
@@ -3154,7 +3154,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="str">
-        <v>Apr 13</v>
+        <v>148</v>
       </c>
       <c r="C17" s="7">
         <v>460.30277779828714</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="str">
-        <v>May 13</v>
+        <v>149</v>
       </c>
       <c r="C18" s="7">
         <v>460.30277779828714</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="str">
-        <v>Jun 13</v>
+        <v>150</v>
       </c>
       <c r="C19" s="7">
         <v>460.30277779828714</v>
@@ -3214,7 +3214,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="str">
-        <v>Jul 13</v>
+        <v>151</v>
       </c>
       <c r="C20" s="7">
         <v>460.30277779828714</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="str">
-        <v>Aug 13</v>
+        <v>152</v>
       </c>
       <c r="C21" s="7">
         <v>460.30277779828714</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="str">
-        <v>Sep 13</v>
+        <v>153</v>
       </c>
       <c r="C22" s="7">
         <v>460.30277779828714</v>
@@ -3274,7 +3274,7 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="str">
-        <v>Oct 13</v>
+        <v>154</v>
       </c>
       <c r="C23" s="7">
         <v>460.30277779828714</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="str">
-        <v>Nov 13</v>
+        <v>155</v>
       </c>
       <c r="C24" s="7">
         <v>460.30277779828714</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="str">
-        <v>Dec 13</v>
+        <v>156</v>
       </c>
       <c r="C25" s="7">
         <v>460.30277779828714</v>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="str">
-        <v>Jan 14</v>
+        <v>157</v>
       </c>
       <c r="C26" s="7">
         <v>460.30277779828714</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="str">
-        <v>Feb 14</v>
+        <v>158</v>
       </c>
       <c r="C27" s="7">
         <v>460.30277779828714</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="str">
-        <v>Mar 14</v>
+        <v>159</v>
       </c>
       <c r="C28" s="7">
         <v>460.30277779828714</v>
@@ -3394,7 +3394,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="str">
-        <v>Apr 14</v>
+        <v>160</v>
       </c>
       <c r="C29" s="7">
         <v>460.30277779828714</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="str">
-        <v>May 14</v>
+        <v>161</v>
       </c>
       <c r="C30" s="7">
         <v>460.30277779828714</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="str">
-        <v>Jun 14</v>
+        <v>162</v>
       </c>
       <c r="C31" s="7">
         <v>460.30277779828714</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="str">
-        <v>Jul 14</v>
+        <v>163</v>
       </c>
       <c r="C32" s="7">
         <v>460.30277779828714</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="str">
-        <v>Aug 14</v>
+        <v>164</v>
       </c>
       <c r="C33" s="7">
         <v>460.30277779828714</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="str">
-        <v>Sep 14</v>
+        <v>165</v>
       </c>
       <c r="C34" s="7">
         <v>460.30277779828714</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="str">
-        <v>Oct 14</v>
+        <v>166</v>
       </c>
       <c r="C35" s="7">
         <v>460.30277779828714</v>
@@ -3534,7 +3534,7 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="str">
-        <v>Nov 14</v>
+        <v>167</v>
       </c>
       <c r="C36" s="7">
         <v>460.30277779828714</v>
@@ -3554,7 +3554,7 @@
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="str">
-        <v>Dec 14</v>
+        <v>168</v>
       </c>
       <c r="C37" s="7">
         <v>460.30277779828714</v>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D3" s="9" cm="1">
         <f t="array" ref="D3">_xll.RScript.Evaluate("frequency(Passengers)")</f>
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D4" s="9" cm="1">
         <f t="array" ref="D4">_xll.RScript.Evaluate("frequency(Passengers)")</f>
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -3775,482 +3775,482 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="str">
-        <v>Jan 13</v>
+        <v>145</v>
       </c>
       <c r="C23" s="7">
         <v>432.0345206025458</v>
       </c>
       <c r="D23" s="7">
-        <v>371.25552790145827</v>
+        <v>373.40418521067613</v>
       </c>
       <c r="E23" s="7">
-        <v>493.43922973397508</v>
+        <v>492.77415854076276</v>
       </c>
       <c r="F23" s="7">
-        <v>341.16545270196696</v>
+        <v>339.05802517440873</v>
       </c>
       <c r="G23" s="7">
-        <v>520.77798152670778</v>
+        <v>525.27897339388801</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="str">
-        <v>Feb 13</v>
+        <v>146</v>
       </c>
       <c r="C24" s="7">
         <v>432.07324171052812</v>
       </c>
       <c r="D24" s="7">
-        <v>351.12699235133215</v>
+        <v>347.91303437662862</v>
       </c>
       <c r="E24" s="7">
-        <v>519.22031482576324</v>
+        <v>519.37954670473698</v>
       </c>
       <c r="F24" s="7">
-        <v>310.42006356260356</v>
+        <v>310.67996789415406</v>
       </c>
       <c r="G24" s="7">
-        <v>569.08149806525876</v>
+        <v>567.86055551518575</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="str">
-        <v>Mar 13</v>
+        <v>147</v>
       </c>
       <c r="C25" s="7">
         <v>432.11049246927291</v>
       </c>
       <c r="D25" s="7">
-        <v>331.87846851194172</v>
+        <v>329.72106765710862</v>
       </c>
       <c r="E25" s="7">
-        <v>538.44190042388584</v>
+        <v>542.05743379947592</v>
       </c>
       <c r="F25" s="7">
-        <v>288.54418790814185</v>
+        <v>286.1407953952048</v>
       </c>
       <c r="G25" s="7">
-        <v>605.43372841063456</v>
+        <v>602.96893508485721</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="str">
-        <v>Apr 13</v>
+        <v>148</v>
       </c>
       <c r="C26" s="7">
         <v>432.14632859216886</v>
       </c>
       <c r="D26" s="7">
-        <v>317.26477807735091</v>
+        <v>315.48659192488736</v>
       </c>
       <c r="E26" s="7">
-        <v>557.8220057723762</v>
+        <v>562.49117389010928</v>
       </c>
       <c r="F26" s="7">
-        <v>269.61263082142818</v>
+        <v>269.97786238579147</v>
       </c>
       <c r="G26" s="7">
-        <v>638.92346239755409</v>
+        <v>641.84723041732548</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="6" t="str">
-        <v>May 13</v>
+        <v>149</v>
       </c>
       <c r="C27" s="7">
         <v>432.18080369050796</v>
       </c>
       <c r="D27" s="7">
-        <v>304.98696006018241</v>
+        <v>301.20994032454746</v>
       </c>
       <c r="E27" s="7">
-        <v>574.01101290042584</v>
+        <v>569.33394116561556</v>
       </c>
       <c r="F27" s="7">
-        <v>254.46038156122776</v>
+        <v>252.61392548127037</v>
       </c>
       <c r="G27" s="7">
-        <v>674.60205813236746</v>
+        <v>668.15476485472368</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="6" t="str">
-        <v>Jun 13</v>
+        <v>150</v>
       </c>
       <c r="C28" s="7">
         <v>432.21396935212897</v>
       </c>
       <c r="D28" s="7">
-        <v>291.71514848332413</v>
+        <v>294.35381464591154</v>
       </c>
       <c r="E28" s="7">
-        <v>591.6367433191956</v>
+        <v>590.42355552335493</v>
       </c>
       <c r="F28" s="7">
-        <v>242.95286400881719</v>
+        <v>241.19738446672844</v>
       </c>
       <c r="G28" s="7">
-        <v>698.81726234634175</v>
+        <v>692.07372760507519</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="6" t="str">
-        <v>Jul 13</v>
+        <v>151</v>
       </c>
       <c r="C29" s="7">
         <v>432.24587521716984</v>
       </c>
       <c r="D29" s="7">
-        <v>283.01738395699527</v>
+        <v>283.35876630255012</v>
       </c>
       <c r="E29" s="7">
-        <v>603.28472459499585</v>
+        <v>599.34911448110222</v>
       </c>
       <c r="F29" s="7">
-        <v>232.80138050907843</v>
+        <v>229.32822779724765</v>
       </c>
       <c r="G29" s="7">
-        <v>724.18507818092348</v>
+        <v>718.79958871044084</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="str">
-        <v>Aug 13</v>
+        <v>152</v>
       </c>
       <c r="C30" s="7">
         <v>432.27656905102936</v>
       </c>
       <c r="D30" s="7">
-        <v>274.91316030690575</v>
+        <v>274.02251846982887</v>
       </c>
       <c r="E30" s="7">
-        <v>614.74774720423682</v>
+        <v>610.18577158578296</v>
       </c>
       <c r="F30" s="7">
-        <v>221.47791369433213</v>
+        <v>220.24125952435355</v>
       </c>
       <c r="G30" s="7">
-        <v>749.25047576644852</v>
+        <v>757.89768949440543</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="str">
-        <v>Sep 13</v>
+        <v>153</v>
       </c>
       <c r="C31" s="7">
         <v>432.30609681463972</v>
       </c>
       <c r="D31" s="7">
-        <v>267.04609093489091</v>
+        <v>264.28838178477309</v>
       </c>
       <c r="E31" s="7">
-        <v>630.69077553957254</v>
+        <v>622.93959248914518</v>
       </c>
       <c r="F31" s="7">
-        <v>213.10992229042873</v>
+        <v>206.06809970397148</v>
       </c>
       <c r="G31" s="7">
-        <v>776.61752481648523</v>
+        <v>771.59496004753919</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="str">
-        <v>Oct 13</v>
+        <v>154</v>
       </c>
       <c r="C32" s="7">
         <v>432.33450273214413</v>
       </c>
       <c r="D32" s="7">
-        <v>261.35418952684358</v>
+        <v>258.09645958121655</v>
       </c>
       <c r="E32" s="7">
-        <v>639.13275487756971</v>
+        <v>632.62775097501867</v>
       </c>
       <c r="F32" s="7">
-        <v>202.93621433023492</v>
+        <v>196.14902334751815</v>
       </c>
       <c r="G32" s="7">
-        <v>800.82001724942791</v>
+        <v>799.13353766979844</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="str">
-        <v>Nov 13</v>
+        <v>155</v>
       </c>
       <c r="C33" s="7">
         <v>432.36182935607303</v>
       </c>
       <c r="D33" s="7">
-        <v>255.28108413274919</v>
+        <v>251.70936941389476</v>
       </c>
       <c r="E33" s="7">
-        <v>652.30949910789343</v>
+        <v>649.79502205093013</v>
       </c>
       <c r="F33" s="7">
-        <v>193.81472993752396</v>
+        <v>189.35315662986551</v>
       </c>
       <c r="G33" s="7">
-        <v>834.08021941093739</v>
+        <v>822.28437831470796</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="str">
-        <v>Dec 13</v>
+        <v>156</v>
       </c>
       <c r="C34" s="7">
         <v>432.3881176301087</v>
       </c>
       <c r="D34" s="7">
-        <v>247.47219204856884</v>
+        <v>245.87974681595082</v>
       </c>
       <c r="E34" s="7">
-        <v>655.95430355449321</v>
+        <v>659.20911420088635</v>
       </c>
       <c r="F34" s="7">
-        <v>190.81421534783146</v>
+        <v>183.82744394207526</v>
       </c>
       <c r="G34" s="7">
-        <v>843.71610486218401</v>
+        <v>840.56115112212296</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="6" t="str">
-        <v>Jan 14</v>
+        <v>157</v>
       </c>
       <c r="C35" s="7">
         <v>432.41340694952407</v>
       </c>
       <c r="D35" s="7">
-        <v>243.00122804211674</v>
+        <v>239.18371647989773</v>
       </c>
       <c r="E35" s="7">
-        <v>670.60626616287686</v>
+        <v>667.72191535110517</v>
       </c>
       <c r="F35" s="7">
-        <v>185.35151331491616</v>
+        <v>179.94020394636908</v>
       </c>
       <c r="G35" s="7">
-        <v>863.91725425485504</v>
+        <v>865.74831660176233</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="str">
-        <v>Feb 14</v>
+        <v>158</v>
       </c>
       <c r="C36" s="7">
         <v>432.43773521938112</v>
       </c>
       <c r="D36" s="7">
-        <v>238.05217817896863</v>
+        <v>234.0704968843952</v>
       </c>
       <c r="E36" s="7">
-        <v>680.1695302973983</v>
+        <v>671.27191616027335</v>
       </c>
       <c r="F36" s="7">
-        <v>176.25569956825871</v>
+        <v>174.35695671163694</v>
       </c>
       <c r="G36" s="7">
-        <v>888.56386860434839</v>
+        <v>891.70468169950675</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="str">
-        <v>Mar 14</v>
+        <v>159</v>
       </c>
       <c r="C37" s="7">
         <v>432.46113891056814</v>
       </c>
       <c r="D37" s="7">
-        <v>233.23888975339349</v>
+        <v>228.46711064841401</v>
       </c>
       <c r="E37" s="7">
-        <v>690.82269291788566</v>
+        <v>677.45408294288666</v>
       </c>
       <c r="F37" s="7">
-        <v>170.75750059276055</v>
+        <v>166.00569388519853</v>
       </c>
       <c r="G37" s="7">
-        <v>903.30072089468763</v>
+        <v>910.80746677022876</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="str">
-        <v>Apr 14</v>
+        <v>160</v>
       </c>
       <c r="C38" s="7">
         <v>432.48365311375443</v>
       </c>
       <c r="D38" s="7">
-        <v>227.86020498172172</v>
+        <v>221.84267027432827</v>
       </c>
       <c r="E38" s="7">
-        <v>688.74233662860456</v>
+        <v>687.74887500939781</v>
       </c>
       <c r="F38" s="7">
-        <v>166.5636506258316</v>
+        <v>159.7191740168596</v>
       </c>
       <c r="G38" s="7">
-        <v>920.03176452486537</v>
+        <v>954.38481806501545</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="str">
-        <v>May 14</v>
+        <v>161</v>
       </c>
       <c r="C39" s="7">
         <v>432.50531159133971</v>
       </c>
       <c r="D39" s="7">
-        <v>221.56133107646139</v>
+        <v>216.04757620107327</v>
       </c>
       <c r="E39" s="7">
-        <v>696.9927270910697</v>
+        <v>699.48433175030095</v>
       </c>
       <c r="F39" s="7">
-        <v>159.39638843487188</v>
+        <v>153.22578651724194</v>
       </c>
       <c r="G39" s="7">
-        <v>948.62161332367282</v>
+        <v>959.15797137815866</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="str">
-        <v>Jun 14</v>
+        <v>162</v>
       </c>
       <c r="C40" s="7">
         <v>432.52614682746747</v>
       </c>
       <c r="D40" s="7">
-        <v>216.66822097517951</v>
+        <v>210.23281086590384</v>
       </c>
       <c r="E40" s="7">
-        <v>701.6706956511116</v>
+        <v>706.49288632246692</v>
       </c>
       <c r="F40" s="7">
-        <v>153.5296138546409</v>
+        <v>149.3125270433919</v>
       </c>
       <c r="G40" s="7">
-        <v>975.81432115956</v>
+        <v>976.06850734213958</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="6" t="str">
-        <v>Jul 14</v>
+        <v>163</v>
       </c>
       <c r="C41" s="7">
         <v>432.54619007617686</v>
       </c>
       <c r="D41" s="7">
-        <v>212.62023318227091</v>
+        <v>207.89276487655411</v>
       </c>
       <c r="E41" s="7">
-        <v>711.83084957882534</v>
+        <v>718.9197619878862</v>
       </c>
       <c r="F41" s="7">
-        <v>149.73865763099951</v>
+        <v>147.50021503110099</v>
       </c>
       <c r="G41" s="7">
-        <v>974.19171577969109</v>
+        <v>998.86670986243735</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="str">
-        <v>Aug 14</v>
+        <v>164</v>
       </c>
       <c r="C42" s="7">
         <v>432.56547140775746</v>
       </c>
       <c r="D42" s="7">
-        <v>207.48911825372988</v>
+        <v>204.61229998313729</v>
       </c>
       <c r="E42" s="7">
-        <v>715.48200706871785</v>
+        <v>717.6769381629789</v>
       </c>
       <c r="F42" s="7">
-        <v>146.28881067790593</v>
+        <v>142.87941288154045</v>
       </c>
       <c r="G42" s="7">
-        <v>986.62034652725174</v>
+        <v>1019.5250510270459</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="6" t="str">
-        <v>Sep 14</v>
+        <v>165</v>
       </c>
       <c r="C43" s="7">
         <v>432.58401975337557</v>
       </c>
       <c r="D43" s="7">
-        <v>203.10033874451801</v>
+        <v>199.99219848823188</v>
       </c>
       <c r="E43" s="7">
-        <v>723.63556783486547</v>
+        <v>726.54142020576614</v>
       </c>
       <c r="F43" s="7">
-        <v>142.77519704087734</v>
+        <v>139.63624608840436</v>
       </c>
       <c r="G43" s="7">
-        <v>1015.887858190104</v>
+        <v>1037.0193954115805</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="str">
-        <v>Oct 14</v>
+        <v>166</v>
       </c>
       <c r="C44" s="7">
         <v>432.60186294803236</v>
       </c>
       <c r="D44" s="7">
-        <v>196.68884212438587</v>
+        <v>195.55940890055268</v>
       </c>
       <c r="E44" s="7">
-        <v>729.22920124634879</v>
+        <v>731.71407417954367</v>
       </c>
       <c r="F44" s="7">
-        <v>139.02243987970672</v>
+        <v>134.91860220634464</v>
       </c>
       <c r="G44" s="7">
-        <v>1026.9266355873997</v>
+        <v>1065.0464360005226</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="6" t="str">
-        <v>Nov 14</v>
+        <v>167</v>
       </c>
       <c r="C45" s="7">
         <v>432.61902777191756</v>
       </c>
       <c r="D45" s="7">
-        <v>192.02681777132671</v>
+        <v>190.27283106955468</v>
       </c>
       <c r="E45" s="7">
-        <v>731.93715408045955</v>
+        <v>731.59897235208132</v>
       </c>
       <c r="F45" s="7">
-        <v>134.59184819963303</v>
+        <v>130.92450781175469</v>
       </c>
       <c r="G45" s="7">
-        <v>1037.9461877857079</v>
+        <v>1079.545516437111</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="6" t="str">
-        <v>Dec 14</v>
+        <v>168</v>
       </c>
       <c r="C46" s="7">
         <v>432.63553999021588</v>
       </c>
       <c r="D46" s="7">
-        <v>189.39667924648151</v>
+        <v>186.09262635748047</v>
       </c>
       <c r="E46" s="7">
-        <v>735.86928129986575</v>
+        <v>745.01814823144741</v>
       </c>
       <c r="F46" s="7">
-        <v>129.50335451699894</v>
+        <v>130.04044840779528</v>
       </c>
       <c r="G46" s="7">
-        <v>1065.1404060654675</v>
+        <v>1120.5886087238437</v>
       </c>
     </row>
   </sheetData>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="D4" s="9" cm="1">
         <f t="array" ref="D4">_xll.RScript.Evaluate("frequency(Passengers)")</f>
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
@@ -4977,7 +4977,7 @@
         <v>12.108532903495451</v>
       </c>
       <c r="I4">
-        <v>1.1462836454292276</v>
+        <v>1.4197839888086368</v>
       </c>
       <c r="J4">
         <v>0.71439592175174416</v>
@@ -5028,16 +5028,16 @@
         <v>25.744479596402833</v>
       </c>
       <c r="G7">
-        <v>1.2071614662984278E-2</v>
+        <v>1.2071614662984287E-2</v>
       </c>
       <c r="H7" s="10">
         <v>9.0279373308108788</v>
       </c>
       <c r="I7">
-        <v>0.80375385684133727</v>
+        <v>0.99552746952017446</v>
       </c>
       <c r="J7">
-        <v>0.30261485064057803</v>
+        <v>0.30261485064057797</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
